--- a/容器表.xlsx
+++ b/容器表.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="50">
   <si>
     <t>姓名</t>
   </si>
@@ -204,6 +204,42 @@
   </si>
   <si>
     <t>ssh lulaoshi@172.16.192.54 -p 10008</t>
+  </si>
+  <si>
+    <t>陈婕</t>
+  </si>
+  <si>
+    <t>chenjie</t>
+  </si>
+  <si>
+    <t>ssh chenjie@172.16.192.54 -p 10010</t>
+  </si>
+  <si>
+    <t>毛建林</t>
+  </si>
+  <si>
+    <t>maojianlin</t>
+  </si>
+  <si>
+    <t>ssh maojianlin@172.16.192.54 -p 10011</t>
+  </si>
+  <si>
+    <t>李辉</t>
+  </si>
+  <si>
+    <t>lihui</t>
+  </si>
+  <si>
+    <t>ssh lihui@172.16.192.54 -p 10012</t>
+  </si>
+  <si>
+    <t>张力人</t>
+  </si>
+  <si>
+    <t>zlr</t>
+  </si>
+  <si>
+    <t>ssh zlr@172.16.192.54 -p 10013</t>
   </si>
   <si>
     <t>ubuntu</t>
@@ -1242,7 +1278,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="18.6388888888889" customWidth="1"/>
@@ -1421,43 +1457,124 @@
       </c>
       <c r="F10" s="8"/>
     </row>
-    <row r="11" ht="18" spans="1:6">
-      <c r="A11" s="10"/>
+    <row r="11" customFormat="1" ht="18" spans="1:6">
+      <c r="A11" s="9"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
     </row>
     <row r="12" ht="18" spans="1:6">
-      <c r="A12" s="10"/>
+      <c r="A12" s="9" t="s">
+        <v>35</v>
+      </c>
       <c r="B12" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="10"/>
+        <v>36</v>
+      </c>
+      <c r="C12" s="10">
+        <v>10010</v>
+      </c>
       <c r="D12" s="10"/>
       <c r="E12" s="10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-    </row>
-    <row r="14" ht="20.4" spans="1:6">
-      <c r="A14" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
+    </row>
+    <row r="13" ht="18" spans="1:6">
+      <c r="A13" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="10">
+        <v>10011</v>
+      </c>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" ht="18" spans="1:6">
+      <c r="A14" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="10">
+        <v>10012</v>
+      </c>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" ht="18" spans="1:6">
+      <c r="A15" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="10">
+        <v>10013</v>
+      </c>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" ht="18" spans="1:6">
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+    </row>
+    <row r="17" ht="18" spans="1:5">
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+    </row>
+    <row r="18" ht="18" spans="1:5">
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+    </row>
+    <row r="19" ht="18" spans="1:5">
+      <c r="A19" s="10"/>
+      <c r="B19" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+    </row>
+    <row r="21" ht="20.4" spans="1:5">
+      <c r="A21" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A21:E21"/>
     <mergeCell ref="F3:F10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
